--- a/ClosedXML.Tests/Resource/Examples/Misc/SheetViews.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/SheetViews.xlsx
@@ -520,7 +520,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AZ2000"/>
+  <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/ClosedXML.Tests/Resource/Examples/Misc/SheetViews.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/SheetViews.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
     <x:t>ZoomScale</x:t>
   </x:si>
@@ -384,7 +384,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -406,7 +406,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -428,7 +428,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -450,7 +450,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -494,7 +494,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>

--- a/ClosedXML.Tests/Resource/Examples/Misc/SheetViews.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/SheetViews.xlsx
@@ -6,13 +6,13 @@
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="ZoomScale" sheetId="2" r:id="rId2"/>
-    <x:sheet name="ZoomScaleNormal" sheetId="3" r:id="rId3"/>
-    <x:sheet name="ZoomScalePageLayoutView" sheetId="4" r:id="rId4"/>
-    <x:sheet name="ZoomScaleSheetLayoutView" sheetId="5" r:id="rId5"/>
-    <x:sheet name="ZoomScaleTooSmall" sheetId="6" r:id="rId6"/>
-    <x:sheet name="ZoomScaleTooBig" sheetId="7" r:id="rId7"/>
-    <x:sheet name="TopLeftCell" sheetId="8" r:id="rId8"/>
+    <x:sheet name="ZoomScale" sheetId="1" r:id="rId2"/>
+    <x:sheet name="ZoomScaleNormal" sheetId="2" r:id="rId3"/>
+    <x:sheet name="ZoomScalePageLayoutView" sheetId="3" r:id="rId4"/>
+    <x:sheet name="ZoomScaleSheetLayoutView" sheetId="4" r:id="rId5"/>
+    <x:sheet name="ZoomScaleTooSmall" sheetId="5" r:id="rId6"/>
+    <x:sheet name="ZoomScaleTooBig" sheetId="6" r:id="rId7"/>
+    <x:sheet name="TopLeftCell" sheetId="7" r:id="rId8"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
